--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-diopsis.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-diopsis.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>240.2626187801361</v>
+        <v>1053.023834228516</v>
       </c>
       <c r="D2" t="n">
-        <v>6.71999979019165</v>
+        <v>15.47000026702881</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3177158093970755</v>
+        <v>0.5088366221737217</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7395143508911133</v>
+        <v>0.7935051321983337</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6882184147834778</v>
+        <v>0.7332691550254822</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6892086267471313</v>
+        <v>0.7340553402900696</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6914408802986145</v>
+        <v>0.7346348762512207</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2437781989574432</v>
+        <v>0.1790616512298584</v>
       </c>
       <c r="K2" t="n">
-        <v>75.54587435722351</v>
+        <v>870.0708768367767</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0861192952602281</v>
+        <v>0.1033951404991499</v>
       </c>
       <c r="M2" t="n">
-        <v>0.179420945841238</v>
+        <v>0.5324232053319249</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1684038114110264</v>
+        <v>0.2319233001918967</v>
       </c>
       <c r="O2" t="n">
-        <v>9.387003183364868</v>
+        <v>11.27007031440735</v>
       </c>
       <c r="P2" t="n">
-        <v>19.55688309669494</v>
+        <v>58.03412938117981</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.35601544380188</v>
+        <v>25.27963972091675</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-165222</t>
+          <t>20250726-004402</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>234.1794447898865</v>
+        <v>1054.395579576492</v>
       </c>
       <c r="D3" t="n">
-        <v>6.739999771118164</v>
+        <v>15.68000030517578</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3094990706962088</v>
+        <v>0.508385228144156</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7472845911979675</v>
+        <v>0.7884333729743958</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7051126956939697</v>
+        <v>0.7280192971229553</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7055972814559937</v>
+        <v>0.7266152501106262</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7063974738121033</v>
+        <v>0.7233316898345947</v>
       </c>
       <c r="J3" t="n">
-        <v>0.246112048625946</v>
+        <v>0.1789789050817489</v>
       </c>
       <c r="K3" t="n">
-        <v>82.38516020774841</v>
+        <v>598.5097410678864</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0802400790223287</v>
+        <v>0.1020680217567933</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1696735959534251</v>
+        <v>0.5238578735141579</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1713396562348812</v>
+        <v>0.2268404763772947</v>
       </c>
       <c r="O3" t="n">
-        <v>8.746168613433838</v>
+        <v>11.12541437149048</v>
       </c>
       <c r="P3" t="n">
-        <v>18.49442195892334</v>
+        <v>57.10050821304321</v>
       </c>
       <c r="Q3" t="n">
-        <v>18.67602252960205</v>
+        <v>24.72561192512512</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-165907</t>
+          <t>20250726-011833</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -841,53 +841,53 @@
         <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>342.1935665607452</v>
+        <v>997.3994898796082</v>
       </c>
       <c r="D4" t="n">
-        <v>6.869999885559082</v>
+        <v>15.4399995803833</v>
       </c>
       <c r="E4" t="n">
-        <v>0.300355270079204</v>
+        <v>0.5080123833247594</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7571633458137512</v>
+        <v>0.7754386067390442</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7125151753425598</v>
+        <v>0.7491686344146729</v>
       </c>
       <c r="H4" t="n">
-        <v>0.713555634021759</v>
+        <v>0.7481024861335754</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7165124416351318</v>
+        <v>0.7412826418876648</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2290800064802169</v>
+        <v>0.1805175691843032</v>
       </c>
       <c r="K4" t="n">
-        <v>72.72934436798096</v>
+        <v>486.6217930316925</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0838525535863473</v>
+        <v>0.1013098069287221</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1710254205476253</v>
+        <v>0.5257151498707062</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1720163165976148</v>
+        <v>0.2437299522784871</v>
       </c>
       <c r="O4" t="n">
-        <v>9.139928340911863</v>
+        <v>11.04276895523071</v>
       </c>
       <c r="P4" t="n">
-        <v>18.64177083969116</v>
+        <v>57.30295133590698</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.74977850914001</v>
+        <v>26.5665647983551</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-170540</t>
+          <t>20250726-014831</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>316.9371409416199</v>
+        <v>1168.385647296906</v>
       </c>
       <c r="D5" t="n">
-        <v>6.599999904632568</v>
+        <v>15.47000026702881</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3044320326298475</v>
+        <v>0.5091314330333616</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7630434632301331</v>
+        <v>0.7866666913032532</v>
       </c>
       <c r="G5" t="n">
-        <v>0.71299809217453</v>
+        <v>0.7486810684204102</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7134724855422974</v>
+        <v>0.7470630407333374</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7088788151741028</v>
+        <v>0.7367125749588013</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2324225455522537</v>
+        <v>0.1796562671661377</v>
       </c>
       <c r="K5" t="n">
-        <v>83.71060466766357</v>
+        <v>513.2366247177124</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0829584664161052</v>
+        <v>0.1020217882383854</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1679962665662853</v>
+        <v>0.5239342002693667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1761828825014446</v>
+        <v>0.2302655648747715</v>
       </c>
       <c r="O5" t="n">
-        <v>9.042472839355469</v>
+        <v>11.12037491798401</v>
       </c>
       <c r="P5" t="n">
-        <v>18.3115930557251</v>
+        <v>57.10882782936096</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.20393419265747</v>
+        <v>25.0989465713501</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-171402</t>
+          <t>20250726-021541</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>235.411361694336</v>
+        <v>1330.56826543808</v>
       </c>
       <c r="D6" t="n">
-        <v>7.050000190734863</v>
+        <v>15.47000026702881</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3122749419316001</v>
+        <v>0.5088422323795075</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7463116049766541</v>
+        <v>0.7929165363311768</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6911457180976868</v>
+        <v>0.7352436780929565</v>
       </c>
       <c r="H6" t="n">
-        <v>0.690316379070282</v>
+        <v>0.7367660999298096</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6885088086128235</v>
+        <v>0.7327268123626709</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2339448034763336</v>
+        <v>0.180743008852005</v>
       </c>
       <c r="K6" t="n">
-        <v>71.56907510757446</v>
+        <v>421.8137998580933</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0825603380115754</v>
+        <v>0.1039735177241334</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1729609791291963</v>
+        <v>0.5346869547432715</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1713756508783463</v>
+        <v>0.2269319678665301</v>
       </c>
       <c r="O6" t="n">
-        <v>8.999076843261719</v>
+        <v>11.33311343193054</v>
       </c>
       <c r="P6" t="n">
-        <v>18.8527467250824</v>
+        <v>58.2808780670166</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.67994594573974</v>
+        <v>24.73558449745178</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-172200</t>
+          <t>20250726-024608</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>629.491149187088</v>
+        <v>2418.732943058014</v>
       </c>
       <c r="D2" t="n">
-        <v>9.850000381469728</v>
+        <v>20.78000068664551</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3123613451466416</v>
+        <v>1.825015740516858</v>
       </c>
       <c r="F2" t="n">
-        <v>0.77689528465271</v>
+        <v>0.8245373368263245</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7252747416496277</v>
+        <v>0.7972696423530579</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7262730002403259</v>
+        <v>0.7978116869926453</v>
       </c>
       <c r="I2" t="n">
-        <v>0.720319926738739</v>
+        <v>0.4899546205997467</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1306212395429611</v>
+        <v>0.4124221801757812</v>
       </c>
       <c r="K2" t="n">
-        <v>778.6438431739807</v>
+        <v>684.368013381958</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0943152226439309</v>
+        <v>0.1545565500171906</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5242665776418983</v>
+        <v>0.2829480718035216</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2288334894617763</v>
+        <v>0.2187029396722076</v>
       </c>
       <c r="O2" t="n">
-        <v>10.28035926818848</v>
+        <v>16.84666395187378</v>
       </c>
       <c r="P2" t="n">
-        <v>57.14505696296692</v>
+        <v>30.84133982658386</v>
       </c>
       <c r="Q2" t="n">
-        <v>24.94285035133361</v>
+        <v>23.83862042427063</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-080231</t>
+          <t>20250724-191314</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>776.4316737651825</v>
+        <v>3050.518273591995</v>
       </c>
       <c r="D3" t="n">
-        <v>9.840000152587891</v>
+        <v>20.98999977111816</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3127490754534558</v>
+        <v>1.890887791911761</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7752808928489685</v>
+        <v>0.8282557725906372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7419589161872864</v>
+        <v>0.7988429069519043</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7362962961196899</v>
+        <v>0.7983996272087097</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7221373915672302</v>
+        <v>0.7932355999946594</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1298950910568237</v>
+        <v>0.3932746350765228</v>
       </c>
       <c r="K3" t="n">
-        <v>544.4380798339844</v>
+        <v>683.8742768764496</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09617157157407979</v>
+        <v>0.1524407601137773</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5252779842516698</v>
+        <v>0.281506087801872</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2601427616329368</v>
+        <v>0.2568009249660947</v>
       </c>
       <c r="O3" t="n">
-        <v>10.48270130157471</v>
+        <v>16.61604285240173</v>
       </c>
       <c r="P3" t="n">
-        <v>57.25530028343201</v>
+        <v>30.68416357040405</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.35556101799011</v>
+        <v>27.99130082130432</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-082814</t>
+          <t>20250724-200706</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>592.9059422016144</v>
+        <v>1718.731165409088</v>
       </c>
       <c r="D4" t="n">
-        <v>9.819999694824221</v>
+        <v>20.36000061035156</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3110968797437606</v>
+        <v>1.888043355058741</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7815340161323547</v>
+        <v>0.8094117641448975</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7442646622657776</v>
+        <v>0.7696728706359863</v>
       </c>
       <c r="H4" t="n">
-        <v>0.745239794254303</v>
+        <v>0.7666362524032593</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7362884879112244</v>
+        <v>0.7577696442604065</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1304670870304107</v>
+        <v>0.4032926559448242</v>
       </c>
       <c r="K4" t="n">
-        <v>410.071665763855</v>
+        <v>679.623640537262</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0990643698141115</v>
+        <v>0.1476683857244089</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5329438437015639</v>
+        <v>0.2767657774304031</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2259327381029041</v>
+        <v>0.2479047359676536</v>
       </c>
       <c r="O4" t="n">
-        <v>10.79801630973816</v>
+        <v>16.09585404396057</v>
       </c>
       <c r="P4" t="n">
-        <v>58.09087896347046</v>
+        <v>30.16746973991394</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.62666845321656</v>
+        <v>27.02161622047424</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-085245</t>
+          <t>20250724-211134</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>735.9349575042725</v>
+        <v>1370.521681070328</v>
       </c>
       <c r="D5" t="n">
-        <v>9.779999732971191</v>
+        <v>21.51000022888184</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3112538426350325</v>
+        <v>1.766216229308735</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7904012203216553</v>
+        <v>0.8121041655540466</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7522847652435303</v>
+        <v>0.7664779424667358</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7432432174682617</v>
+        <v>0.7676630616188049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7247494459152222</v>
+        <v>0.7642905712127686</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1316469758749008</v>
+        <v>0.4009049236774444</v>
       </c>
       <c r="K5" t="n">
-        <v>559.8559198379517</v>
+        <v>788.7553308010101</v>
       </c>
       <c r="L5" t="n">
-        <v>0.098058444644333</v>
+        <v>0.1502337368256455</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5327680985861962</v>
+        <v>0.2813436897522812</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2279695327128839</v>
+        <v>0.249099919555384</v>
       </c>
       <c r="O5" t="n">
-        <v>10.6883704662323</v>
+        <v>16.37547731399536</v>
       </c>
       <c r="P5" t="n">
-        <v>58.07172274589539</v>
+        <v>30.66646218299866</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.84867906570435</v>
+        <v>27.15189123153687</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-091155</t>
+          <t>20250724-215343</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>807.9512422084808</v>
+        <v>2815.806839942932</v>
       </c>
       <c r="D6" t="n">
-        <v>9.779999732971191</v>
+        <v>21.38999938964844</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3105012296244155</v>
+        <v>1.842917847633362</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7955603003501892</v>
+        <v>0.8223525285720825</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7287644743919373</v>
+        <v>0.7966673970222473</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7288657426834106</v>
+        <v>0.7974826097488403</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7228155136108398</v>
+        <v>0.8009029626846313</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1289132088422775</v>
+        <v>0.4087209105491638</v>
       </c>
       <c r="K6" t="n">
-        <v>504.6588761806488</v>
+        <v>685.0959160327911</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0990797664047381</v>
+        <v>0.1531687876500121</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5292826792515746</v>
+        <v>0.2798032366901363</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2264699892166557</v>
+        <v>0.2593100027206841</v>
       </c>
       <c r="O6" t="n">
-        <v>10.79969453811646</v>
+        <v>16.69539785385132</v>
       </c>
       <c r="P6" t="n">
-        <v>57.69181203842163</v>
+        <v>30.49855279922485</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.68522882461548</v>
+        <v>28.26479029655457</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-093558</t>
+          <t>20250724-223205</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>1312.110051631927</v>
+        <v>3257.263331651688</v>
       </c>
       <c r="D2" t="n">
-        <v>15.39000034332275</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="E2" t="n">
-        <v>1.850151151418686</v>
+        <v>1.615345034334395</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7903732061386108</v>
+        <v>0.8125845789909363</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7709270715713501</v>
+        <v>0.7898373007774353</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7662517428398132</v>
+        <v>0.7896292805671692</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7682303786277771</v>
+        <v>0.782250702381134</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4148474037647247</v>
+        <v>0.4023699760437011</v>
       </c>
       <c r="K2" t="n">
-        <v>804.4161701202393</v>
+        <v>225.0348773002625</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1591438306580989</v>
+        <v>0.1531362686682185</v>
       </c>
       <c r="M2" t="n">
-        <v>0.280130946308101</v>
+        <v>0.3224678148917101</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2488061856786045</v>
+        <v>0.2442706309327292</v>
       </c>
       <c r="O2" t="n">
-        <v>17.34667754173279</v>
+        <v>16.69185328483582</v>
       </c>
       <c r="P2" t="n">
-        <v>30.53427314758301</v>
+        <v>35.14899182319641</v>
       </c>
       <c r="Q2" t="n">
-        <v>27.1198742389679</v>
+        <v>26.62549877166748</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-153808</t>
+          <t>20250727-035711</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>1124.662372350693</v>
+        <v>5085.853680849075</v>
       </c>
       <c r="D3" t="n">
-        <v>15.6899995803833</v>
+        <v>10.94999980926514</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8524569272995</v>
+        <v>1.671903120387684</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8108680248260498</v>
+        <v>0.7986554503440857</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7576375007629395</v>
+        <v>0.7772685885429382</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7586206793785095</v>
+        <v>0.778437614440918</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7593457698822021</v>
+        <v>0.7682058215141296</v>
       </c>
       <c r="J3" t="n">
-        <v>0.397779107093811</v>
+        <v>0.4123137891292572</v>
       </c>
       <c r="K3" t="n">
-        <v>740.5830914974213</v>
+        <v>220.6980233192444</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1551293386231868</v>
+        <v>0.1584668968795636</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2775880874843772</v>
+        <v>0.310660344745041</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2537991606861079</v>
+        <v>0.3673064861822566</v>
       </c>
       <c r="O3" t="n">
-        <v>16.90909790992737</v>
+        <v>17.27289175987244</v>
       </c>
       <c r="P3" t="n">
-        <v>30.25710153579712</v>
+        <v>33.86197757720947</v>
       </c>
       <c r="Q3" t="n">
-        <v>27.66410851478577</v>
+        <v>40.03640699386597</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-161538</t>
+          <t>20250727-045727</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>1448.302632331848</v>
+        <v>2229.638315200806</v>
       </c>
       <c r="D4" t="n">
-        <v>15.60000038146973</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>1.832837654196698</v>
+        <v>1.378636794430869</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8056637048721313</v>
+        <v>0.822597324848175</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7718579173088074</v>
+        <v>0.7902286052703857</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7673336267471313</v>
+        <v>0.788612425327301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7680000066757202</v>
+        <v>0.7887640595436096</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4120741784572601</v>
+        <v>0.4130899608135223</v>
       </c>
       <c r="K4" t="n">
-        <v>763.5570240020752</v>
+        <v>214.2524929046631</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1567071337218678</v>
+        <v>0.154964048928077</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2780858879789299</v>
+        <v>0.3086679397373024</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2525033732073022</v>
+        <v>0.4943194214357148</v>
       </c>
       <c r="O4" t="n">
-        <v>17.08107757568359</v>
+        <v>16.8910813331604</v>
       </c>
       <c r="P4" t="n">
-        <v>30.31136178970337</v>
+        <v>33.64480543136597</v>
       </c>
       <c r="Q4" t="n">
-        <v>27.52286767959595</v>
+        <v>53.88081693649292</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-164856</t>
+          <t>20250727-062818</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>1338.414374351502</v>
+        <v>3291.028662204742</v>
       </c>
       <c r="D5" t="n">
-        <v>15.48999977111816</v>
+        <v>10.47000026702881</v>
       </c>
       <c r="E5" t="n">
-        <v>1.812989229247684</v>
+        <v>1.685517171451024</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8115016222000122</v>
+        <v>0.8244169950485229</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7609242796897888</v>
+        <v>0.7939204573631287</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7617215514183044</v>
+        <v>0.7920746803283691</v>
       </c>
       <c r="I5" t="n">
-        <v>0.759671151638031</v>
+        <v>0.7873429656028748</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4079017639160156</v>
+        <v>0.3978815376758575</v>
       </c>
       <c r="K5" t="n">
-        <v>726.4034559726715</v>
+        <v>229.401844739914</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1559595186775977</v>
+        <v>0.1491107350095696</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2777017978353238</v>
+        <v>0.3032026487752932</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2539861858437914</v>
+        <v>0.3556124267228153</v>
       </c>
       <c r="O5" t="n">
-        <v>16.99958753585815</v>
+        <v>16.25307011604309</v>
       </c>
       <c r="P5" t="n">
-        <v>30.26949596405029</v>
+        <v>33.04908871650696</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.68449425697327</v>
+        <v>38.76175451278687</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-172801</t>
+          <t>20250727-071152</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
-        <v>1068.368654251099</v>
+        <v>3544.981572628021</v>
       </c>
       <c r="D6" t="n">
-        <v>15.46000003814697</v>
+        <v>11.61999988555908</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8667551279068</v>
+        <v>1.537768747748398</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7941176295280457</v>
+        <v>0.8230027556419373</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7735254168510437</v>
+        <v>0.8019625544548035</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7695863246917725</v>
+        <v>0.7962151169776917</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7737765312194824</v>
+        <v>0.7895818948745728</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3989217281341553</v>
+        <v>0.4182847440242767</v>
       </c>
       <c r="K6" t="n">
-        <v>703.1619148254395</v>
+        <v>209.526116847992</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1561866506524042</v>
+        <v>0.158708872051414</v>
       </c>
       <c r="M6" t="n">
-        <v>0.28792385005076</v>
+        <v>0.3123921385598839</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2604561726981347</v>
+        <v>0.2454823047742931</v>
       </c>
       <c r="O6" t="n">
-        <v>17.02434492111206</v>
+        <v>17.29926705360413</v>
       </c>
       <c r="P6" t="n">
-        <v>31.38369965553284</v>
+        <v>34.05074310302734</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.38972282409668</v>
+        <v>26.75757122039795</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-180439</t>
+          <t>20250727-081305</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>1279.559430122375</v>
+        <v>2512.988522291183</v>
       </c>
       <c r="D2" t="n">
-        <v>9.829999923706056</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E2" t="n">
-        <v>1.302805177867413</v>
+        <v>1.410857241600752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7870967984199524</v>
+        <v>0.7800546288490295</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7461538314819336</v>
+        <v>0.7468637824058533</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7454091906547546</v>
+        <v>0.7463851571083069</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7359563112258911</v>
+        <v>0.7484220266342163</v>
       </c>
       <c r="J2" t="n">
-        <v>0.384001761674881</v>
+        <v>0.3994642496109009</v>
       </c>
       <c r="K2" t="n">
-        <v>302.9016251564026</v>
+        <v>90.64578557014464</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1522096997007317</v>
+        <v>0.1442293967675725</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3017968212792632</v>
+        <v>0.2843447431511835</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2470758376865212</v>
+        <v>0.2131193121638867</v>
       </c>
       <c r="O2" t="n">
-        <v>16.59085726737976</v>
+        <v>15.7210042476654</v>
       </c>
       <c r="P2" t="n">
-        <v>32.8958535194397</v>
+        <v>30.993577003479</v>
       </c>
       <c r="Q2" t="n">
-        <v>26.93126630783081</v>
+        <v>23.23000502586365</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-043109</t>
+          <t>20250728-065526</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>1400.001189470291</v>
+        <v>3108.359570264816</v>
       </c>
       <c r="D3" t="n">
-        <v>10.52000045776367</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="E3" t="n">
-        <v>1.459490299224854</v>
+        <v>1.35662163466942</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7997193932533264</v>
+        <v>0.7997298240661621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7591011524200439</v>
+        <v>0.7564045190811157</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7569460868835449</v>
+        <v>0.7543190717697144</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7498235106468201</v>
+        <v>0.7409458160400391</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3962967097759247</v>
+        <v>0.38651242852211</v>
       </c>
       <c r="K3" t="n">
-        <v>243.8016903400421</v>
+        <v>100.5091948509216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1582691078885979</v>
+        <v>0.1369096401634566</v>
       </c>
       <c r="M3" t="n">
-        <v>0.306619316066077</v>
+        <v>0.1923649354812202</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3156414994406044</v>
+        <v>0.1951056182931322</v>
       </c>
       <c r="O3" t="n">
-        <v>17.25133275985718</v>
+        <v>14.92315077781677</v>
       </c>
       <c r="P3" t="n">
-        <v>33.42150545120239</v>
+        <v>20.967777967453</v>
       </c>
       <c r="Q3" t="n">
-        <v>34.40492343902588</v>
+        <v>21.26651239395142</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-045944</t>
+          <t>20250728-074044</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>1759.896110773086</v>
+        <v>2758.70373415947</v>
       </c>
       <c r="D4" t="n">
-        <v>10.84000015258789</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="E4" t="n">
-        <v>1.42653957435063</v>
+        <v>1.365360127554999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7992021441459656</v>
+        <v>0.7879000902175903</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7725499272346497</v>
+        <v>0.7607443332672119</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7724043130874634</v>
+        <v>0.7614720463752747</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7558435797691345</v>
+        <v>0.7433881163597107</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3991438448429107</v>
+        <v>0.3952504396438598</v>
       </c>
       <c r="K4" t="n">
-        <v>256.2673563957214</v>
+        <v>103.0557653903961</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1592954889349981</v>
+        <v>0.1468041971189166</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3029922367235936</v>
+        <v>0.2058220850218326</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2764768206745113</v>
+        <v>0.1940821485781888</v>
       </c>
       <c r="O4" t="n">
-        <v>17.36320829391479</v>
+        <v>16.00165748596191</v>
       </c>
       <c r="P4" t="n">
-        <v>33.0261538028717</v>
+        <v>22.43460726737976</v>
       </c>
       <c r="Q4" t="n">
-        <v>30.13597345352173</v>
+        <v>21.15495419502258</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-052927</t>
+          <t>20250728-083555</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>1388.412883996964</v>
+        <v>2669.440375089645</v>
       </c>
       <c r="D5" t="n">
-        <v>10.03999996185303</v>
+        <v>5.46999979019165</v>
       </c>
       <c r="E5" t="n">
-        <v>1.449675664305687</v>
+        <v>1.405007537673501</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7971014380455017</v>
+        <v>0.7859135270118713</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7727975249290466</v>
+        <v>0.758948802947998</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7705408334732056</v>
+        <v>0.7545372247695923</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7682333588600159</v>
+        <v>0.7499419450759888</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4107324481010437</v>
+        <v>0.3938846290111542</v>
       </c>
       <c r="K5" t="n">
-        <v>235.9813561439514</v>
+        <v>90.7508625984192</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1559719558155864</v>
+        <v>0.1431385508371055</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3124334484065345</v>
+        <v>0.1979582703441655</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2414145557158584</v>
+        <v>0.2380168766056725</v>
       </c>
       <c r="O5" t="n">
-        <v>17.00094318389893</v>
+        <v>15.60210204124451</v>
       </c>
       <c r="P5" t="n">
-        <v>34.05524587631226</v>
+        <v>21.57745146751404</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.31418657302856</v>
+        <v>25.94383955001831</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-060529</t>
+          <t>20250728-092522</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>1731.30298447609</v>
+        <v>3584.815484046936</v>
       </c>
       <c r="D6" t="n">
-        <v>10.39999961853027</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="E6" t="n">
-        <v>1.567711397221214</v>
+        <v>1.338078690071901</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7979729771614075</v>
+        <v>0.7843273282051086</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7821452617645264</v>
+        <v>0.7524890303611755</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7826874852180481</v>
+        <v>0.7526100873947144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7824903726577759</v>
+        <v>0.7490774989128113</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4036075472831726</v>
+        <v>0.4046094715595245</v>
       </c>
       <c r="K6" t="n">
-        <v>262.0260500907898</v>
+        <v>91.46398162841795</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1599126015234431</v>
+        <v>0.1471728316140831</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3141115739804889</v>
+        <v>0.1965839687837373</v>
       </c>
       <c r="N6" t="n">
-        <v>0.243622534865633</v>
+        <v>0.1967942670944633</v>
       </c>
       <c r="O6" t="n">
-        <v>17.4304735660553</v>
+        <v>16.04183864593506</v>
       </c>
       <c r="P6" t="n">
-        <v>34.23816156387329</v>
+        <v>21.42765259742737</v>
       </c>
       <c r="Q6" t="n">
-        <v>26.554856300354</v>
+        <v>21.45057511329651</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-063446</t>
+          <t>20250728-101321</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>1500.457865953445</v>
+        <v>2784.150416851044</v>
       </c>
       <c r="D2" t="n">
-        <v>3.380000114440918</v>
+        <v>7.590000152587891</v>
       </c>
       <c r="E2" t="n">
-        <v>1.371646755620053</v>
+        <v>1.408062502316066</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7714782357215881</v>
+        <v>0.8140326738357544</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7569023370742798</v>
+        <v>0.7933012247085571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7557252049446106</v>
+        <v>0.7913702130317688</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7411144375801086</v>
+        <v>0.7841792702674866</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3962360620498657</v>
+        <v>0.389323353767395</v>
       </c>
       <c r="K2" t="n">
-        <v>96.86471724510191</v>
+        <v>223.1395921707153</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1486753848714566</v>
+        <v>0.1509880953972492</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2419632399847748</v>
+        <v>0.2393352547916797</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2963523011688792</v>
+        <v>0.2330297089497977</v>
       </c>
       <c r="O2" t="n">
-        <v>16.20561695098877</v>
+        <v>16.45770239830017</v>
       </c>
       <c r="P2" t="n">
-        <v>26.37399315834045</v>
+        <v>26.08754277229309</v>
       </c>
       <c r="Q2" t="n">
-        <v>32.30240082740784</v>
+        <v>25.40023827552796</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-182416</t>
+          <t>20250729-104139</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>1487.550228595734</v>
+        <v>1652.038655996323</v>
       </c>
       <c r="D3" t="n">
-        <v>3.470000028610229</v>
+        <v>8.310000419616699</v>
       </c>
       <c r="E3" t="n">
-        <v>1.535507861305686</v>
+        <v>1.527703329136497</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7737588882446289</v>
+        <v>0.8024606704711914</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7494336366653442</v>
+        <v>0.7589305639266968</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7473179697990417</v>
+        <v>0.7575687766075134</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7350993156433105</v>
+        <v>0.7634508609771729</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3972161412239074</v>
+        <v>0.3985251188278198</v>
       </c>
       <c r="K3" t="n">
-        <v>113.1949458122253</v>
+        <v>167.3083064556122</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1436884053256533</v>
+        <v>0.1521057142030208</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2914477641429376</v>
+        <v>0.2442270287679969</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3188865884728388</v>
+        <v>0.2248199139166316</v>
       </c>
       <c r="O3" t="n">
-        <v>15.66203618049622</v>
+        <v>16.57952284812927</v>
       </c>
       <c r="P3" t="n">
-        <v>31.7678062915802</v>
+        <v>26.62074613571167</v>
       </c>
       <c r="Q3" t="n">
-        <v>34.75863814353943</v>
+        <v>24.50537061691284</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-185245</t>
+          <t>20250729-113338</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>1367.590475320816</v>
+        <v>2290.816198348999</v>
       </c>
       <c r="D4" t="n">
-        <v>3.660000085830689</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="E4" t="n">
-        <v>1.496196426451206</v>
+        <v>1.445206650665828</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7534722089767456</v>
+        <v>0.818769097328186</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7320466637611389</v>
+        <v>0.7782482504844666</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7340975403785706</v>
+        <v>0.7650429606437683</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7249602675437927</v>
+        <v>0.7686387896537781</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4058312475681305</v>
+        <v>0.3686327934265136</v>
       </c>
       <c r="K4" t="n">
-        <v>114.7582757472992</v>
+        <v>163.407500743866</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1513454236021829</v>
+        <v>0.1475046818409491</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2104922565845174</v>
+        <v>0.2353198331430417</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2016358244309731</v>
+        <v>0.2187093704118641</v>
       </c>
       <c r="O4" t="n">
-        <v>16.49665117263794</v>
+        <v>16.07801032066345</v>
       </c>
       <c r="P4" t="n">
-        <v>22.9436559677124</v>
+        <v>25.64986181259156</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.97830486297608</v>
+        <v>23.83932137489319</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-192135</t>
+          <t>20250729-120551</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>1304.912447929382</v>
+        <v>2696.212146997452</v>
       </c>
       <c r="D5" t="n">
-        <v>3.359999895095825</v>
+        <v>8.010000228881836</v>
       </c>
       <c r="E5" t="n">
-        <v>1.408021733164787</v>
+        <v>1.404773533344269</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7523061037063599</v>
+        <v>0.803094208240509</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7294930815696716</v>
+        <v>0.7796609997749329</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7272307872772217</v>
+        <v>0.7714352607727051</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7075538635253906</v>
+        <v>0.7707641124725342</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3997422754764557</v>
+        <v>0.4040683805942535</v>
       </c>
       <c r="K5" t="n">
-        <v>97.94244313240053</v>
+        <v>153.9318923950195</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1518794287235365</v>
+        <v>0.1497131728251046</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2016084981620858</v>
+        <v>0.2425448128936487</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2061437116850406</v>
+        <v>0.2244877552767412</v>
       </c>
       <c r="O5" t="n">
-        <v>16.55485773086548</v>
+        <v>16.3187358379364</v>
       </c>
       <c r="P5" t="n">
-        <v>21.97532629966736</v>
+        <v>26.43738460540771</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.46966457366944</v>
+        <v>24.46916532516479</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-194757</t>
+          <t>20250729-124834</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>1247.694984436035</v>
+        <v>2758.945685148239</v>
       </c>
       <c r="D6" t="n">
-        <v>3.789999961853027</v>
+        <v>8.859999656677246</v>
       </c>
       <c r="E6" t="n">
-        <v>1.334078125655651</v>
+        <v>1.353265235821406</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7746818065643311</v>
+        <v>0.8202828764915466</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7336028814315796</v>
+        <v>0.7958257794380188</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7346847057342529</v>
+        <v>0.7935571670532227</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7330130338668823</v>
+        <v>0.7885352969169617</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4022779166698456</v>
+        <v>0.3859053552150726</v>
       </c>
       <c r="K6" t="n">
-        <v>92.4636812210083</v>
+        <v>166.4800214767456</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1521927435463721</v>
+        <v>0.1431748254583516</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1967746445892054</v>
+        <v>0.2393763852775643</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5335214859848723</v>
+        <v>0.2259088393745072</v>
       </c>
       <c r="O6" t="n">
-        <v>16.58900904655457</v>
+        <v>15.60605597496033</v>
       </c>
       <c r="P6" t="n">
-        <v>21.44843626022339</v>
+        <v>26.09202599525452</v>
       </c>
       <c r="Q6" t="n">
-        <v>58.15384197235107</v>
+        <v>24.62406349182129</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-201258</t>
+          <t>20250729-133756</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="C2" t="n">
-        <v>1432.767153978348</v>
+        <v>1816.828722715378</v>
       </c>
       <c r="D2" t="n">
-        <v>7.309999942779541</v>
+        <v>10.68000030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>1.35242239634196</v>
+        <v>0.8437269693845278</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8063604235649109</v>
+        <v>0.7485460042953491</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7845584750175476</v>
+        <v>0.7094642519950867</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7854176163673401</v>
+        <v>0.7065895795822144</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7824084758758545</v>
+        <v>0.7108851671218872</v>
       </c>
       <c r="J2" t="n">
-        <v>0.413595050573349</v>
+        <v>0.1975287646055221</v>
       </c>
       <c r="K2" t="n">
-        <v>216.5245878696442</v>
+        <v>69.44680285453796</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1530879462530853</v>
+        <v>0.1023773272103125</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2715872012147116</v>
+        <v>0.1690359903038095</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2520718377664548</v>
+        <v>0.1674635957140441</v>
       </c>
       <c r="O2" t="n">
-        <v>16.6865861415863</v>
+        <v>11.15912866592407</v>
       </c>
       <c r="P2" t="n">
-        <v>29.60300493240356</v>
+        <v>18.42492294311523</v>
       </c>
       <c r="Q2" t="n">
-        <v>27.47583031654358</v>
+        <v>18.25353193283081</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-065459</t>
+          <t>20250730-101034</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
-        <v>1353.771605014801</v>
+        <v>1654.318011522293</v>
       </c>
       <c r="D3" t="n">
-        <v>7.550000190734863</v>
+        <v>10.67000007629394</v>
       </c>
       <c r="E3" t="n">
-        <v>1.440975457429886</v>
+        <v>0.8279557328828624</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7910552024841309</v>
+        <v>0.7743285894393921</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7659192681312561</v>
+        <v>0.710659921169281</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7590002417564392</v>
+        <v>0.7113328576087952</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7503493428230286</v>
+        <v>0.7133000493049622</v>
       </c>
       <c r="J3" t="n">
-        <v>0.412704735994339</v>
+        <v>0.2402665317058563</v>
       </c>
       <c r="K3" t="n">
-        <v>228.3969099521637</v>
+        <v>60.20632433891296</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1565441319701868</v>
+        <v>0.1015041224453427</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2668646869309451</v>
+        <v>0.1738113700796704</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6575318039010424</v>
+        <v>0.1692845865127143</v>
       </c>
       <c r="O3" t="n">
-        <v>17.06331038475037</v>
+        <v>11.06394934654236</v>
       </c>
       <c r="P3" t="n">
-        <v>29.08825087547302</v>
+        <v>18.94543933868408</v>
       </c>
       <c r="Q3" t="n">
-        <v>71.67096662521362</v>
+        <v>18.45201992988586</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-072427</t>
+          <t>20250730-104323</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="C4" t="n">
-        <v>1411.736981391907</v>
+        <v>2381.880527734756</v>
       </c>
       <c r="D4" t="n">
-        <v>8.25</v>
+        <v>10.67000007629394</v>
       </c>
       <c r="E4" t="n">
-        <v>1.519484296441078</v>
+        <v>0.845407487142204</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8049365878105164</v>
+        <v>0.7712100148200989</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7717086672782898</v>
+        <v>0.7213978171348572</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7714552283287048</v>
+        <v>0.7193694710731506</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7594819664955139</v>
+        <v>0.7198090553283691</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3951533734798431</v>
+        <v>0.2267449051141739</v>
       </c>
       <c r="K4" t="n">
-        <v>174.9618194103241</v>
+        <v>60.02121019363403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1549886891601282</v>
+        <v>0.1008796429415361</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2368348847835436</v>
+        <v>0.176244516985132</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2283668649305991</v>
+        <v>0.1719840688442965</v>
       </c>
       <c r="O4" t="n">
-        <v>16.89376711845398</v>
+        <v>10.99588108062744</v>
       </c>
       <c r="P4" t="n">
-        <v>25.81500244140625</v>
+        <v>19.21065235137939</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.8919882774353</v>
+        <v>18.74626350402832</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-075331</t>
+          <t>20250730-111333</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="C5" t="n">
-        <v>1561.207294225693</v>
+        <v>2027.95592045784</v>
       </c>
       <c r="D5" t="n">
-        <v>7.059999942779541</v>
+        <v>10.57999992370606</v>
       </c>
       <c r="E5" t="n">
-        <v>1.417082560689826</v>
+        <v>0.8444976293763449</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8055943846702576</v>
+        <v>0.7546119093894958</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7882300615310669</v>
+        <v>0.7031686902046204</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7848042845726013</v>
+        <v>0.7002840638160706</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7805445790290833</v>
+        <v>0.7010260224342346</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3936094343662262</v>
+        <v>0.2368649989366531</v>
       </c>
       <c r="K5" t="n">
-        <v>157.0891361236572</v>
+        <v>59.97375869750977</v>
       </c>
       <c r="L5" t="n">
-        <v>0.147620450466051</v>
+        <v>0.0999356081726354</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2348311603616137</v>
+        <v>0.1734834701643077</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2349932784334235</v>
+        <v>0.1710238150500376</v>
       </c>
       <c r="O5" t="n">
-        <v>16.09062910079956</v>
+        <v>10.89298129081726</v>
       </c>
       <c r="P5" t="n">
-        <v>25.59659647941589</v>
+        <v>18.90969824790954</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.61426734924316</v>
+        <v>18.6415958404541</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-082149</t>
+          <t>20250730-115550</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>2352.52838754654</v>
+        <v>1467.652723312378</v>
       </c>
       <c r="D6" t="n">
-        <v>7.78000020980835</v>
+        <v>10.64999961853027</v>
       </c>
       <c r="E6" t="n">
-        <v>1.376805746555329</v>
+        <v>0.8454478681087494</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8117443919181824</v>
+        <v>0.7375125885009766</v>
       </c>
       <c r="G6" t="n">
-        <v>0.787712037563324</v>
+        <v>0.6912000179290771</v>
       </c>
       <c r="H6" t="n">
-        <v>0.78779536485672</v>
+        <v>0.6931869983673096</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7752577066421509</v>
+        <v>0.6916802525520325</v>
       </c>
       <c r="J6" t="n">
-        <v>0.403891384601593</v>
+        <v>0.2587564587593078</v>
       </c>
       <c r="K6" t="n">
-        <v>158.76442694664</v>
+        <v>70.93103718757629</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1523023723462306</v>
+        <v>0.1042778316987763</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2364973190727584</v>
+        <v>0.1697676575511967</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2465138894702316</v>
+        <v>0.1751585312939565</v>
       </c>
       <c r="O6" t="n">
-        <v>16.60095858573914</v>
+        <v>11.36628365516663</v>
       </c>
       <c r="P6" t="n">
-        <v>25.77820777893066</v>
+        <v>18.50467467308044</v>
       </c>
       <c r="Q6" t="n">
-        <v>26.87001395225525</v>
+        <v>19.09227991104126</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-085231</t>
+          <t>20250730-123212</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>733.7229635715485</v>
+        <v>811.6560513973236</v>
       </c>
       <c r="D2" t="n">
-        <v>2.240000009536743</v>
+        <v>13.84000015258789</v>
       </c>
       <c r="E2" t="n">
-        <v>0.478424591422081</v>
+        <v>0.4605804899973528</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7572540640830994</v>
+        <v>0.8205658793449402</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7165775299072266</v>
+        <v>0.8158628344535828</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7019962072372437</v>
+        <v>0.7381128072738647</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7084203362464905</v>
+        <v>0.7343941330909729</v>
       </c>
       <c r="J2" t="n">
-        <v>0.263290137052536</v>
+        <v>0.1680008471012115</v>
       </c>
       <c r="K2" t="n">
-        <v>49.90193367004395</v>
+        <v>101.0723836421967</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1158430598197727</v>
+        <v>0.1170346365062468</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1755013203402178</v>
+        <v>0.2122114842091131</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1696186568758903</v>
+        <v>0.1778560734670096</v>
       </c>
       <c r="O2" t="n">
-        <v>12.62689352035522</v>
+        <v>12.75677537918091</v>
       </c>
       <c r="P2" t="n">
-        <v>19.12964391708374</v>
+        <v>23.13105177879333</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.48843359947205</v>
+        <v>19.38631200790405</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-194412</t>
+          <t>20250731-030633</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
-        <v>510.7541000843048</v>
+        <v>1007.050410985947</v>
       </c>
       <c r="D3" t="n">
-        <v>2.349999904632568</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4713431077344077</v>
+        <v>0.4599886066477063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7316725850105286</v>
+        <v>0.8266574740409851</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7016184329986572</v>
+        <v>0.8155255317687988</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6725376844406128</v>
+        <v>0.7256814241409302</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6545810699462891</v>
+        <v>0.7237237095832825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2400339990854263</v>
+        <v>0.1738892197608947</v>
       </c>
       <c r="K3" t="n">
-        <v>40.49163150787354</v>
+        <v>100.5541844367981</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1107820786467386</v>
+        <v>0.1188634863687217</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1769463622241938</v>
+        <v>0.2149094397868585</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1630172707618923</v>
+        <v>0.1771899188330414</v>
       </c>
       <c r="O3" t="n">
-        <v>12.07524657249451</v>
+        <v>12.95612001419067</v>
       </c>
       <c r="P3" t="n">
-        <v>19.28715348243713</v>
+        <v>23.42512893676757</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.76888251304626</v>
+        <v>19.31370115280152</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-195832</t>
+          <t>20250731-032335</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" t="n">
-        <v>915.6562032699584</v>
+        <v>927.5363903045654</v>
       </c>
       <c r="D4" t="n">
-        <v>2.420000076293945</v>
+        <v>13.94999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4784565976550502</v>
+        <v>0.4643668000514691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7689582109451294</v>
+        <v>0.8154059648513794</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7473490238189697</v>
+        <v>0.8070403933525085</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7237697243690491</v>
+        <v>0.7233616709709167</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7293736934661865</v>
+        <v>0.7167630195617676</v>
       </c>
       <c r="J4" t="n">
-        <v>0.258754163980484</v>
+        <v>0.1756397187709808</v>
       </c>
       <c r="K4" t="n">
-        <v>39.77635097503662</v>
+        <v>111.1052658557892</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112143472793999</v>
+        <v>0.1179791196770624</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1808691987203895</v>
+        <v>0.2086558801318527</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1720798868651784</v>
+        <v>0.1813677888397776</v>
       </c>
       <c r="O4" t="n">
-        <v>12.2236385345459</v>
+        <v>12.8597240447998</v>
       </c>
       <c r="P4" t="n">
-        <v>19.71474266052246</v>
+        <v>22.74349093437195</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.75670766830444</v>
+        <v>19.76908898353577</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-200910</t>
+          <t>20250731-034343</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>817.7940020561218</v>
+        <v>754.6326932907104</v>
       </c>
       <c r="D5" t="n">
-        <v>2.359999895095825</v>
+        <v>14.03999996185303</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4787744571055685</v>
+        <v>0.4618518897947275</v>
       </c>
       <c r="F5" t="n">
-        <v>0.744343101978302</v>
+        <v>0.8258913159370422</v>
       </c>
       <c r="G5" t="n">
-        <v>0.718492329120636</v>
+        <v>0.8132196068763733</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6973684430122375</v>
+        <v>0.7340083718299866</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6991981863975525</v>
+        <v>0.7293666005134583</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2357539534568786</v>
+        <v>0.1746103167533874</v>
       </c>
       <c r="K5" t="n">
-        <v>50.42679023742676</v>
+        <v>102.9884076118469</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1101499019412819</v>
+        <v>0.1185330885265945</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1649818748509118</v>
+        <v>0.2109799975648932</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1633724553869404</v>
+        <v>0.1845582297088903</v>
       </c>
       <c r="O5" t="n">
-        <v>12.00633931159973</v>
+        <v>12.9201066493988</v>
       </c>
       <c r="P5" t="n">
-        <v>17.98302435874939</v>
+        <v>22.99681973457336</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.80759763717651</v>
+        <v>20.11684703826904</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-202634</t>
+          <t>20250731-040242</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>664.8417754173279</v>
+        <v>867.2801880836487</v>
       </c>
       <c r="D6" t="n">
-        <v>2.609999895095825</v>
+        <v>13.94999980926514</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4857464222745462</v>
+        <v>0.4537710754140731</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7461174726486206</v>
+        <v>0.818493127822876</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7223587036132812</v>
+        <v>0.8081254363059998</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7091941237449646</v>
+        <v>0.7366125583648682</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7058266401290894</v>
+        <v>0.7279012203216553</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2328030169010162</v>
+        <v>0.1874807476997375</v>
       </c>
       <c r="K6" t="n">
-        <v>39.19269204139709</v>
+        <v>111.1253371238708</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1077158669812963</v>
+        <v>0.1200241101991146</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1786615520442297</v>
+        <v>0.212599489667</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1765229767615642</v>
+        <v>0.1917532343383229</v>
       </c>
       <c r="O6" t="n">
-        <v>11.7410295009613</v>
+        <v>13.08262801170349</v>
       </c>
       <c r="P6" t="n">
-        <v>19.47410917282104</v>
+        <v>23.173344373703</v>
       </c>
       <c r="Q6" t="n">
-        <v>19.24100446701049</v>
+        <v>20.9011025428772</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-204227</t>
+          <t>20250731-041839</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>1821.150205373764</v>
+        <v>240.2626187801361</v>
       </c>
       <c r="D2" t="n">
-        <v>5.769999980926514</v>
+        <v>6.71999979019165</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8437551530924711</v>
+        <v>0.3177158093970755</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7586452960968018</v>
+        <v>0.7395143508911133</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7149032950401306</v>
+        <v>0.6882184147834778</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7092995047569275</v>
+        <v>0.6892086267471313</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7052785754203796</v>
+        <v>0.6914408802986145</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2206845432519912</v>
+        <v>0.2437781989574432</v>
       </c>
       <c r="K2" t="n">
-        <v>57.40034246444702</v>
+        <v>75.54587435722351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1023759623186303</v>
+        <v>0.0861192952602281</v>
       </c>
       <c r="M2" t="n">
-        <v>0.174732604158034</v>
+        <v>0.179420945841238</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1720501676611944</v>
+        <v>0.1684038114110264</v>
       </c>
       <c r="O2" t="n">
-        <v>11.15897989273071</v>
+        <v>9.387003183364868</v>
       </c>
       <c r="P2" t="n">
-        <v>19.04585385322571</v>
+        <v>19.55688309669494</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.75346827507019</v>
+        <v>18.35601544380188</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-093238</t>
+          <t>20250627-165222</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>1687.935534715652</v>
+        <v>234.1794447898865</v>
       </c>
       <c r="D3" t="n">
-        <v>5.630000114440918</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8507960732554046</v>
+        <v>0.3094990706962088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7660036087036133</v>
+        <v>0.7472845911979675</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7192457914352417</v>
+        <v>0.7051126956939697</v>
       </c>
       <c r="H3" t="n">
-        <v>0.715168833732605</v>
+        <v>0.7055972814559937</v>
       </c>
       <c r="I3" t="n">
-        <v>0.715206503868103</v>
+        <v>0.7063974738121033</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2203508764505386</v>
+        <v>0.246112048625946</v>
       </c>
       <c r="K3" t="n">
-        <v>57.46513867378235</v>
+        <v>82.38516020774841</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0997051755222705</v>
+        <v>0.0802400790223287</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1801493845948385</v>
+        <v>0.1696735959534251</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1750419752313456</v>
+        <v>0.1713396562348812</v>
       </c>
       <c r="O3" t="n">
-        <v>10.86786413192749</v>
+        <v>8.746168613433838</v>
       </c>
       <c r="P3" t="n">
-        <v>19.6362829208374</v>
+        <v>18.49442195892334</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.07957530021667</v>
+        <v>18.67602252960205</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-100532</t>
+          <t>20250627-165907</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>2376.971791505814</v>
+        <v>342.1935665607452</v>
       </c>
       <c r="D4" t="n">
-        <v>5.75</v>
+        <v>6.869999885559082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8449073723047087</v>
+        <v>0.300355270079204</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7662291526794434</v>
+        <v>0.7571633458137512</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7130792140960693</v>
+        <v>0.7125151753425598</v>
       </c>
       <c r="H4" t="n">
-        <v>0.708714485168457</v>
+        <v>0.713555634021759</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7133573889732361</v>
+        <v>0.7165124416351318</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2340011894702911</v>
+        <v>0.2290800064802169</v>
       </c>
       <c r="K4" t="n">
-        <v>68.98347353935242</v>
+        <v>72.72934436798096</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1085437350316878</v>
+        <v>0.0838525535863473</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1781064785948587</v>
+        <v>0.1710254205476253</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1770811540271164</v>
+        <v>0.1720163165976148</v>
       </c>
       <c r="O4" t="n">
-        <v>11.83126711845398</v>
+        <v>9.139928340911863</v>
       </c>
       <c r="P4" t="n">
-        <v>19.4136061668396</v>
+        <v>18.64177083969116</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.30184578895569</v>
+        <v>18.74977850914001</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-103554</t>
+          <t>20250627-170540</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C5" t="n">
-        <v>1465.730194568634</v>
+        <v>316.9371409416199</v>
       </c>
       <c r="D5" t="n">
-        <v>5.610000133514404</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="E5" t="n">
-        <v>0.841621168198124</v>
+        <v>0.3044320326298475</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7407145500183105</v>
+        <v>0.7630434632301331</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7014853954315186</v>
+        <v>0.71299809217453</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7013422846794128</v>
+        <v>0.7134724855422974</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6957773566246033</v>
+        <v>0.7088788151741028</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2478627413511276</v>
+        <v>0.2324225455522537</v>
       </c>
       <c r="K5" t="n">
-        <v>67.6634361743927</v>
+        <v>83.71060466766357</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1080046881229505</v>
+        <v>0.0829584664161052</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1740937320464248</v>
+        <v>0.1679962665662853</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1720066617388244</v>
+        <v>0.1761828825014446</v>
       </c>
       <c r="O5" t="n">
-        <v>11.77251100540161</v>
+        <v>9.042472839355469</v>
       </c>
       <c r="P5" t="n">
-        <v>18.9762167930603</v>
+        <v>18.3115930557251</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.74872612953186</v>
+        <v>19.20393419265747</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-111806</t>
+          <t>20250627-171402</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>1731.89536690712</v>
+        <v>235.411361694336</v>
       </c>
       <c r="D6" t="n">
-        <v>5.579999923706055</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8320424000959139</v>
+        <v>0.3122749419316001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7590318918228149</v>
+        <v>0.7463116049766541</v>
       </c>
       <c r="G6" t="n">
-        <v>0.703522264957428</v>
+        <v>0.6911457180976868</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6997860670089722</v>
+        <v>0.690316379070282</v>
       </c>
       <c r="I6" t="n">
-        <v>0.696003794670105</v>
+        <v>0.6885088086128235</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2419798374176025</v>
+        <v>0.2339448034763336</v>
       </c>
       <c r="K6" t="n">
-        <v>68.98712420463562</v>
+        <v>71.56907510757446</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1073767920152856</v>
+        <v>0.0825603380115754</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1781290583654281</v>
+        <v>0.1729609791291963</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1767461124910127</v>
+        <v>0.1713756508783463</v>
       </c>
       <c r="O6" t="n">
-        <v>11.70407032966614</v>
+        <v>8.999076843261719</v>
       </c>
       <c r="P6" t="n">
-        <v>19.41606736183167</v>
+        <v>18.8527467250824</v>
       </c>
       <c r="Q6" t="n">
-        <v>19.26532626152039</v>
+        <v>18.67994594573974</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-114505</t>
+          <t>20250627-172200</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9080,53 +9080,53 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>705.9667525291443</v>
+        <v>733.7229635715485</v>
       </c>
       <c r="D2" t="n">
-        <v>8.529999732971191</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4501748752593994</v>
+        <v>0.478424591422081</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8201240301132202</v>
+        <v>0.7572540640830994</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7981947064399719</v>
+        <v>0.7165775299072266</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7151177525520325</v>
+        <v>0.7019962072372437</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7193775177001953</v>
+        <v>0.7084203362464905</v>
       </c>
       <c r="J2" t="n">
-        <v>0.238436758518219</v>
+        <v>0.263290137052536</v>
       </c>
       <c r="K2" t="n">
-        <v>111.7250163555145</v>
+        <v>49.90193367004395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1333801921354521</v>
+        <v>0.1158430598197727</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2093063122635587</v>
+        <v>0.1755013203402178</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1804767026813752</v>
+        <v>0.1696186568758903</v>
       </c>
       <c r="O2" t="n">
-        <v>14.53844094276428</v>
+        <v>12.62689352035522</v>
       </c>
       <c r="P2" t="n">
-        <v>22.81438803672791</v>
+        <v>19.12964391708374</v>
       </c>
       <c r="Q2" t="n">
-        <v>19.6719605922699</v>
+        <v>18.48843359947205</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-113817</t>
+          <t>20250701-194412</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>788.4055106639862</v>
+        <v>510.7541000843048</v>
       </c>
       <c r="D3" t="n">
-        <v>8.699999809265137</v>
+        <v>2.349999904632568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4516570355210985</v>
+        <v>0.4713431077344077</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8154535889625549</v>
+        <v>0.7316725850105286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8110598921775818</v>
+        <v>0.7016184329986572</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7087303400039673</v>
+        <v>0.6725376844406128</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7085133194923401</v>
+        <v>0.6545810699462891</v>
       </c>
       <c r="J3" t="n">
-        <v>0.232164591550827</v>
+        <v>0.2400339990854263</v>
       </c>
       <c r="K3" t="n">
-        <v>99.82470273971558</v>
+        <v>40.49163150787354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1331582572482048</v>
+        <v>0.1107820786467386</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2069180011749267</v>
+        <v>0.1769463622241938</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1841595129135551</v>
+        <v>0.1630172707618923</v>
       </c>
       <c r="O3" t="n">
-        <v>14.51425004005432</v>
+        <v>12.07524657249451</v>
       </c>
       <c r="P3" t="n">
-        <v>22.55406212806702</v>
+        <v>19.28715348243713</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.07338690757751</v>
+        <v>17.76888251304626</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-115338</t>
+          <t>20250701-195832</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C4" t="n">
-        <v>1102.046401023865</v>
+        <v>915.6562032699584</v>
       </c>
       <c r="D4" t="n">
-        <v>8.520000457763672</v>
+        <v>2.420000076293945</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4480285882949829</v>
+        <v>0.4784565976550502</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8267413377761841</v>
+        <v>0.7689582109451294</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8168449401855469</v>
+        <v>0.7473490238189697</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7288732528686523</v>
+        <v>0.7237697243690491</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7209593057632446</v>
+        <v>0.7293736934661865</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2373015731573104</v>
+        <v>0.258754163980484</v>
       </c>
       <c r="K4" t="n">
-        <v>110.4165925979614</v>
+        <v>39.77635097503662</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1333194697668793</v>
+        <v>0.112143472793999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2119007351201608</v>
+        <v>0.1808691987203895</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1827175573471489</v>
+        <v>0.1720798868651784</v>
       </c>
       <c r="O4" t="n">
-        <v>14.53182220458984</v>
+        <v>12.2236385345459</v>
       </c>
       <c r="P4" t="n">
-        <v>23.09718012809753</v>
+        <v>19.71474266052246</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.91621375083924</v>
+        <v>18.75670766830444</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-121009</t>
+          <t>20250701-200910</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>748.9110143184662</v>
+        <v>817.7940020561218</v>
       </c>
       <c r="D5" t="n">
-        <v>8.779999732971191</v>
+        <v>2.359999895095825</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4553311849540135</v>
+        <v>0.4787744571055685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8223140239715576</v>
+        <v>0.744343101978302</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8141320943832397</v>
+        <v>0.718492329120636</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7308070659637451</v>
+        <v>0.6973684430122375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7277131676673889</v>
+        <v>0.6991981863975525</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2021213322877884</v>
+        <v>0.2357539534568786</v>
       </c>
       <c r="K5" t="n">
-        <v>101.2142379283905</v>
+        <v>50.42679023742676</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1328445421446354</v>
+        <v>0.1101499019412819</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2129395904890987</v>
+        <v>0.1649818748509118</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1871328047656138</v>
+        <v>0.1633724553869404</v>
       </c>
       <c r="O5" t="n">
-        <v>14.48005509376526</v>
+        <v>12.00633931159973</v>
       </c>
       <c r="P5" t="n">
-        <v>23.21041536331177</v>
+        <v>17.98302435874939</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.3974757194519</v>
+        <v>17.80759763717651</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-123204</t>
+          <t>20250701-202634</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>828.0092666149139</v>
+        <v>664.8417754173279</v>
       </c>
       <c r="D6" t="n">
-        <v>8.640000343322754</v>
+        <v>2.609999895095825</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4513814666513669</v>
+        <v>0.4857464222745462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.819918155670166</v>
+        <v>0.7461174726486206</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8073111772537231</v>
+        <v>0.7223587036132812</v>
       </c>
       <c r="H6" t="n">
-        <v>0.737281858921051</v>
+        <v>0.7091941237449646</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7243058681488037</v>
+        <v>0.7058266401290894</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1806561201810836</v>
+        <v>0.2328030169010162</v>
       </c>
       <c r="K6" t="n">
-        <v>110.5302832126617</v>
+        <v>39.19269204139709</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1256422843408147</v>
+        <v>0.1077158669812963</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2110171864885802</v>
+        <v>0.1786615520442297</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1846626482972311</v>
+        <v>0.1765229767615642</v>
       </c>
       <c r="O6" t="n">
-        <v>13.6950089931488</v>
+        <v>11.7410295009613</v>
       </c>
       <c r="P6" t="n">
-        <v>23.00087332725525</v>
+        <v>19.47410917282104</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.1282286643982</v>
+        <v>19.24100446701049</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-124758</t>
+          <t>20250701-204227</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
